--- a/source/BossDrops.xlsx
+++ b/source/BossDrops.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1337c\OneDrive\Skrivbord\Projects\Nebula calc\source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ulrika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5841D9C-4607-48A8-A9FC-D3B88AA103D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B49A6A-A7C6-4B1E-BB96-4241FE87D393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{D55BD798-421B-4B04-AA33-88A80DD2AC5C}"/>
+    <workbookView xWindow="28680" yWindow="-2025" windowWidth="29040" windowHeight="17520" xr2:uid="{D55BD798-421B-4B04-AA33-88A80DD2AC5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Lords" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="20">
   <si>
     <t>Nubhe</t>
   </si>
@@ -85,12 +85,27 @@
   <si>
     <t>Attempts</t>
   </si>
+  <si>
+    <t>Primary Shard</t>
+  </si>
+  <si>
+    <t>Intermediate Shard</t>
+  </si>
+  <si>
+    <t>Advanced Shard</t>
+  </si>
+  <si>
+    <t>Primary Essence</t>
+  </si>
+  <si>
+    <t>Intermediate Essence</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,6 +122,30 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -138,13 +177,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -163,7 +206,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -480,12 +523,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D19CB3BD-8C90-46B6-8962-159A436E4641}">
   <dimension ref="A1:SG64"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="501" width="10.6640625" customWidth="1"/>
+    <col min="1" max="501" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:501" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1990,7 +2033,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2352,7 +2395,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2714,7 +2757,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3076,7 +3119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3330,7 +3373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3458,12 +3501,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:501" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -4968,7 +5011,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -5456,7 +5499,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -5944,7 +5987,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -6432,7 +6475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -6764,7 +6807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -6982,12 +7025,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:501" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
@@ -8492,7 +8535,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="16" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -9097,7 +9140,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -9702,7 +9745,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -10307,7 +10350,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -10777,7 +10820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -11031,12 +11074,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:501" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
@@ -12541,7 +12584,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>1</v>
       </c>
@@ -13155,7 +13198,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>2</v>
       </c>
@@ -13769,7 +13812,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -14383,7 +14426,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -14853,7 +14896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -15113,12 +15156,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:501" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>10</v>
       </c>
@@ -16623,7 +16666,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="30" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>1</v>
       </c>
@@ -17384,7 +17427,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>2</v>
       </c>
@@ -18145,7 +18188,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -18906,7 +18949,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -19496,7 +19539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -19834,12 +19877,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:501" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>11</v>
       </c>
@@ -21344,7 +21387,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>1</v>
       </c>
@@ -22702,7 +22745,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>2</v>
       </c>
@@ -24060,7 +24103,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -25418,7 +25461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -26395,7 +26438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -26919,12 +26962,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:501" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>12</v>
       </c>
@@ -28429,7 +28472,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="44" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>1</v>
       </c>
@@ -29793,7 +29836,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>2</v>
       </c>
@@ -31157,7 +31200,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>3</v>
       </c>
@@ -32521,7 +32564,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -33561,7 +33604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:501" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:501" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -34082,12 +34125,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>13</v>
       </c>
@@ -34113,7 +34156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>14</v>
       </c>
@@ -34139,9 +34182,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>1</v>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="B53">
         <f>SUM(B44:QL44)</f>
@@ -34172,7 +34215,7 @@
         <v>3473</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -34205,9 +34248,9 @@
         <v>29.184873949579831</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>2</v>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="B55">
         <f>SUM(B45:QL45)</f>
@@ -34238,7 +34281,7 @@
         <v>2969</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -34271,9 +34314,9 @@
         <v>24.949579831932773</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>3</v>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="B57">
         <f>SUM(B46:QL46)</f>
@@ -34304,7 +34347,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -34337,9 +34380,9 @@
         <v>3.9327731092436973</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>4</v>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="B59">
         <f>SUM(B47:QL47)</f>
@@ -34370,7 +34413,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -34403,9 +34446,9 @@
         <v>0.96638655462184875</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>5</v>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="B61">
         <f>SUM(B48:QL48)</f>
@@ -34436,7 +34479,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>13</v>
       </c>
@@ -34469,7 +34512,7 @@
         <v>0.34453781512605042</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E64" s="3"/>
     </row>
   </sheetData>

--- a/source/BossDrops.xlsx
+++ b/source/BossDrops.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ulrika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B49A6A-A7C6-4B1E-BB96-4241FE87D393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A9455B-27FC-4C9E-B009-0A643FD18ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2025" windowWidth="29040" windowHeight="17520" xr2:uid="{D55BD798-421B-4B04-AA33-88A80DD2AC5C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D55BD798-421B-4B04-AA33-88A80DD2AC5C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Lords" sheetId="1" r:id="rId1"/>
+    <sheet name="Average" sheetId="2" r:id="rId1"/>
+    <sheet name="Lords" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="20">
   <si>
     <t>Nubhe</t>
   </si>
@@ -521,6 +522,415 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E286823F-BC8F-48AF-A9AF-99A0A99641E4}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="501" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <f>COUNT(Lords!B44:ZX44)</f>
+        <v>453</v>
+      </c>
+      <c r="C2">
+        <f>COUNT(Lords!B37:ZX37)</f>
+        <v>451</v>
+      </c>
+      <c r="D2">
+        <f>COUNT(Lords!B30:ZX30)</f>
+        <v>252</v>
+      </c>
+      <c r="E2">
+        <f>COUNT(Lords!B23:ZX23)</f>
+        <v>203</v>
+      </c>
+      <c r="F2">
+        <f>COUNT(Lords!B16:ZX16)</f>
+        <v>200</v>
+      </c>
+      <c r="G2">
+        <f>COUNT(Lords!B9:ZW9)</f>
+        <v>161</v>
+      </c>
+      <c r="H2">
+        <f>COUNT(Lords!B2:ZX2)</f>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <f>SUM(Lords!B44:ZX44)</f>
+        <v>32152</v>
+      </c>
+      <c r="C3">
+        <f>SUM(Lords!B37:ZX37)</f>
+        <v>28911</v>
+      </c>
+      <c r="D3">
+        <f>SUM(Lords!B30:ZX30)</f>
+        <v>14335</v>
+      </c>
+      <c r="E3">
+        <f>SUM(Lords!B23:ZX23)</f>
+        <v>10148</v>
+      </c>
+      <c r="F3">
+        <f>SUM(Lords!B16:ZW16)</f>
+        <v>8707</v>
+      </c>
+      <c r="G3">
+        <f>SUM(Lords!B9:ZW9)</f>
+        <v>5805</v>
+      </c>
+      <c r="H3">
+        <f>SUM(Lords!B2:ZX2)</f>
+        <v>3473</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2">
+        <f t="shared" ref="B4:H4" si="0">B3/B2</f>
+        <v>70.975717439293604</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" si="0"/>
+        <v>64.104212860310426</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" si="0"/>
+        <v>56.884920634920633</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" si="0"/>
+        <v>49.990147783251231</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
+        <v>43.534999999999997</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" ref="F4:G4" si="1">G3/G2</f>
+        <v>36.055900621118013</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="0"/>
+        <v>29.184873949579831</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <f>SUM(Lords!B45:ZX45)</f>
+        <v>24956</v>
+      </c>
+      <c r="C5">
+        <f>SUM(Lords!B38:ZX38)</f>
+        <v>22595</v>
+      </c>
+      <c r="D5">
+        <f>SUM(Lords!B31:ZX31)</f>
+        <v>11425</v>
+      </c>
+      <c r="E5">
+        <f>SUM(Lords!B24:ZX24)</f>
+        <v>8159</v>
+      </c>
+      <c r="F5">
+        <f>SUM(Lords!B17:ZW17)</f>
+        <v>6976</v>
+      </c>
+      <c r="G5">
+        <f>SUM(Lords!B10:ZW10)</f>
+        <v>4824</v>
+      </c>
+      <c r="H5">
+        <f>SUM(Lords!B3:ZX3)</f>
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2">
+        <f t="shared" ref="B6:H6" si="2">B5/B2</f>
+        <v>55.090507726269315</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="2"/>
+        <v>50.099778270509979</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="2"/>
+        <v>45.337301587301589</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="2"/>
+        <v>40.192118226600982</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="2"/>
+        <v>34.880000000000003</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" ref="F6:G6" si="3">G5/G2</f>
+        <v>29.962732919254659</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="2"/>
+        <v>24.949579831932773</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <f>SUM(Lords!B46:ZX46)</f>
+        <v>7302</v>
+      </c>
+      <c r="C7">
+        <f>SUM(Lords!B39:ZX39)</f>
+        <v>6239</v>
+      </c>
+      <c r="D7">
+        <f>SUM(Lords!B32:ZX32)</f>
+        <v>3088</v>
+      </c>
+      <c r="E7">
+        <f>SUM(Lords!B25:ZX25)</f>
+        <v>2025</v>
+      </c>
+      <c r="F7">
+        <f>SUM(Lords!B18:ZW18)</f>
+        <v>1571</v>
+      </c>
+      <c r="G7">
+        <f>SUM(Lords!B11:ZW11)</f>
+        <v>955</v>
+      </c>
+      <c r="H7">
+        <f>SUM(Lords!B4:ZX4)</f>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2">
+        <f t="shared" ref="B8:H8" si="4">B7/B2</f>
+        <v>16.119205298013245</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="4"/>
+        <v>13.833702882483371</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="4"/>
+        <v>12.253968253968255</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="4"/>
+        <v>9.9753694581280783</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="4"/>
+        <v>7.8550000000000004</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" ref="F8:G8" si="5">G7/G2</f>
+        <v>5.9316770186335406</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="4"/>
+        <v>3.9327731092436973</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <f>SUM(Lords!B47:ZX47)</f>
+        <v>440</v>
+      </c>
+      <c r="C9">
+        <f>SUM(Lords!B40:ZX40)</f>
+        <v>420</v>
+      </c>
+      <c r="D9">
+        <f>SUM(Lords!B33:ZX33)</f>
+        <v>249</v>
+      </c>
+      <c r="E9">
+        <f>SUM(Lords!B26:ZX26)</f>
+        <v>207</v>
+      </c>
+      <c r="F9">
+        <f>SUM(Lords!B19:ZW19)</f>
+        <v>213</v>
+      </c>
+      <c r="G9">
+        <f>SUM(Lords!B12:ZW12)</f>
+        <v>148</v>
+      </c>
+      <c r="H9">
+        <f>SUM(Lords!B5:ZX5)</f>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2">
+        <f t="shared" ref="B10:H10" si="6">B9/B2</f>
+        <v>0.9713024282560706</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="6"/>
+        <v>0.9312638580931264</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="6"/>
+        <v>0.98809523809523814</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0197044334975369</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="6"/>
+        <v>1.0649999999999999</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" ref="F10:G10" si="7">G9/G2</f>
+        <v>0.91925465838509313</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="6"/>
+        <v>0.96638655462184875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <f>SUM(Lords!B48:ZX48)</f>
+        <v>172</v>
+      </c>
+      <c r="C11">
+        <f>SUM(Lords!B41:ZX41)</f>
+        <v>173</v>
+      </c>
+      <c r="D11">
+        <f>SUM(Lords!B34:ZX34)</f>
+        <v>111</v>
+      </c>
+      <c r="E11">
+        <f>SUM(Lords!B27:ZX27)</f>
+        <v>85</v>
+      </c>
+      <c r="F11">
+        <f>SUM(Lords!B20:ZW20)</f>
+        <v>83</v>
+      </c>
+      <c r="G11">
+        <f>SUM(Lords!B13:ZW13)</f>
+        <v>71</v>
+      </c>
+      <c r="H11">
+        <f>SUM(Lords!B6:ZX6)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2">
+        <f t="shared" ref="B12:H12" si="8">B11/B2</f>
+        <v>0.37969094922737306</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="8"/>
+        <v>0.38359201773835921</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="8"/>
+        <v>0.44047619047619047</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="8"/>
+        <v>0.41871921182266009</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="8"/>
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" ref="F12:G12" si="9">G11/G2</f>
+        <v>0.44099378881987578</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="8"/>
+        <v>0.34453781512605042</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E14" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0" right="0" top="0.39410000000000006" bottom="0.39410000000000006" header="0" footer="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CSida &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D19CB3BD-8C90-46B6-8962-159A436E4641}">
   <dimension ref="A1:SG64"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/source/BossDrops.xlsx
+++ b/source/BossDrops.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ulrika\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1337c\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A9455B-27FC-4C9E-B009-0A643FD18ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F8BDCD-F8A3-4361-A042-C9A5856CB93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D55BD798-421B-4B04-AA33-88A80DD2AC5C}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{D55BD798-421B-4B04-AA33-88A80DD2AC5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Average" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="21">
   <si>
     <t>Nubhe</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>Intermediate Essence</t>
+  </si>
+  <si>
+    <t>Dubhe</t>
   </si>
 </sst>
 </file>
@@ -207,7 +210,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -524,12 +527,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E286823F-BC8F-48AF-A9AF-99A0A99641E4}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="501" width="10.625" customWidth="1"/>
+    <col min="1" max="501" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -552,10 +555,10 @@
         <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -588,7 +591,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
@@ -621,7 +624,7 @@
         <v>3473</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -646,7 +649,7 @@
         <v>43.534999999999997</v>
       </c>
       <c r="G4" s="2">
-        <f t="shared" ref="F4:G4" si="1">G3/G2</f>
+        <f t="shared" ref="G4" si="1">G3/G2</f>
         <v>36.055900621118013</v>
       </c>
       <c r="H4" s="2">
@@ -654,7 +657,7 @@
         <v>29.184873949579831</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
@@ -687,7 +690,7 @@
         <v>2969</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -712,7 +715,7 @@
         <v>34.880000000000003</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" ref="F6:G6" si="3">G5/G2</f>
+        <f t="shared" ref="G6" si="3">G5/G2</f>
         <v>29.962732919254659</v>
       </c>
       <c r="H6" s="2">
@@ -720,7 +723,7 @@
         <v>24.949579831932773</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -753,7 +756,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -778,7 +781,7 @@
         <v>7.8550000000000004</v>
       </c>
       <c r="G8" s="2">
-        <f t="shared" ref="F8:G8" si="5">G7/G2</f>
+        <f t="shared" ref="G8" si="5">G7/G2</f>
         <v>5.9316770186335406</v>
       </c>
       <c r="H8" s="2">
@@ -786,7 +789,7 @@
         <v>3.9327731092436973</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
@@ -819,7 +822,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -844,7 +847,7 @@
         <v>1.0649999999999999</v>
       </c>
       <c r="G10" s="2">
-        <f t="shared" ref="F10:G10" si="7">G9/G2</f>
+        <f t="shared" ref="G10" si="7">G9/G2</f>
         <v>0.91925465838509313</v>
       </c>
       <c r="H10" s="2">
@@ -852,7 +855,7 @@
         <v>0.96638655462184875</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
@@ -885,7 +888,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -910,7 +913,7 @@
         <v>0.41499999999999998</v>
       </c>
       <c r="G12" s="2">
-        <f t="shared" ref="F12:G12" si="9">G11/G2</f>
+        <f t="shared" ref="G12" si="9">G11/G2</f>
         <v>0.44099378881987578</v>
       </c>
       <c r="H12" s="2">
@@ -918,7 +921,7 @@
         <v>0.34453781512605042</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="E14" s="3"/>
     </row>
   </sheetData>
@@ -933,12 +936,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D19CB3BD-8C90-46B6-8962-159A436E4641}">
   <dimension ref="A1:SG64"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="501" width="10.625" customWidth="1"/>
+    <col min="1" max="501" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:501" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2443,7 +2446,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2805,7 +2808,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3167,7 +3170,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3529,7 +3532,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3783,7 +3786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3911,12 +3914,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:501" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -5421,7 +5424,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -5909,7 +5912,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -6397,7 +6400,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -6885,7 +6888,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -7217,7 +7220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -7435,12 +7438,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:501" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
@@ -8945,7 +8948,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="16" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -9550,7 +9553,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -10155,7 +10158,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -10760,7 +10763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -11230,7 +11233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -11484,12 +11487,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:501" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
@@ -12994,7 +12997,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1</v>
       </c>
@@ -13608,7 +13611,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>2</v>
       </c>
@@ -14222,7 +14225,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -14836,7 +14839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -15306,7 +15309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -15566,12 +15569,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:501" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>10</v>
       </c>
@@ -17076,7 +17079,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="30" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1</v>
       </c>
@@ -17837,7 +17840,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>2</v>
       </c>
@@ -18598,7 +18601,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -19359,7 +19362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -19949,7 +19952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -20287,12 +20290,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:501" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>11</v>
       </c>
@@ -21797,7 +21800,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1</v>
       </c>
@@ -23155,7 +23158,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>2</v>
       </c>
@@ -24513,7 +24516,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -25871,7 +25874,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -26848,7 +26851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -27372,12 +27375,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:501" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>12</v>
       </c>
@@ -28882,7 +28885,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="44" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>1</v>
       </c>
@@ -30246,7 +30249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>2</v>
       </c>
@@ -31610,7 +31613,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>3</v>
       </c>
@@ -32974,7 +32977,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -34014,7 +34017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:501" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:501" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -34535,12 +34538,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>13</v>
       </c>
@@ -34566,7 +34569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>14</v>
       </c>
@@ -34592,7 +34595,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>15</v>
       </c>
@@ -34625,7 +34628,7 @@
         <v>3473</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -34658,7 +34661,7 @@
         <v>29.184873949579831</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>16</v>
       </c>
@@ -34691,7 +34694,7 @@
         <v>2969</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -34724,7 +34727,7 @@
         <v>24.949579831932773</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>17</v>
       </c>
@@ -34757,7 +34760,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -34790,7 +34793,7 @@
         <v>3.9327731092436973</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>18</v>
       </c>
@@ -34823,7 +34826,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -34856,7 +34859,7 @@
         <v>0.96638655462184875</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>19</v>
       </c>
@@ -34889,7 +34892,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>13</v>
       </c>
@@ -34922,7 +34925,7 @@
         <v>0.34453781512605042</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="E64" s="3"/>
     </row>
   </sheetData>
